--- a/raw/processedSamples/20260518_r9_DB_USDA-whole-blood_Nano-QuIC.xlsx
+++ b/raw/processedSamples/20260518_r9_DB_USDA-whole-blood_Nano-QuIC.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F25DF8-CCF4-4B4A-AD53-44EFD0B56F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4336891-334B-440E-9757-054D7CDCF9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="1" r:id="rId1"/>
     <sheet name="Table All Cycles" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="169">
   <si>
     <t>User: USER</t>
   </si>
@@ -534,12 +534,15 @@
   <si>
     <t>Dilutions</t>
   </si>
+  <si>
+    <t xml:space="preserve"> Raw Data (448-10/482-10)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,6 +557,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -761,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -823,8 +834,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3028,9 +3042,9 @@
         <v>165</v>
       </c>
     </row>
-    <row r="13" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>166</v>
+    <row r="13" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B13" s="19">
         <v>0</v>
@@ -3324,9 +3338,9 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="14" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>166</v>
+    <row r="14" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A14" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B14" s="19">
         <v>0.25</v>
@@ -3620,9 +3634,9 @@
         <v>753</v>
       </c>
     </row>
-    <row r="15" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>166</v>
+    <row r="15" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B15" s="19">
         <v>0.5</v>
@@ -3916,9 +3930,9 @@
         <v>670</v>
       </c>
     </row>
-    <row r="16" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>166</v>
+    <row r="16" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B16" s="19">
         <v>0.75</v>
@@ -4212,9 +4226,9 @@
         <v>619</v>
       </c>
     </row>
-    <row r="17" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>166</v>
+    <row r="17" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
@@ -4508,9 +4522,9 @@
         <v>624</v>
       </c>
     </row>
-    <row r="18" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>166</v>
+    <row r="18" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B18" s="19">
         <v>1.25</v>
@@ -4804,9 +4818,9 @@
         <v>614</v>
       </c>
     </row>
-    <row r="19" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>166</v>
+    <row r="19" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B19" s="19">
         <v>1.5</v>
@@ -5100,9 +5114,9 @@
         <v>632</v>
       </c>
     </row>
-    <row r="20" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>166</v>
+    <row r="20" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A20" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B20" s="19">
         <v>1.75</v>
@@ -5396,9 +5410,9 @@
         <v>598</v>
       </c>
     </row>
-    <row r="21" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>166</v>
+    <row r="21" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A21" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B21" s="19">
         <v>2</v>
@@ -5692,9 +5706,9 @@
         <v>596</v>
       </c>
     </row>
-    <row r="22" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>166</v>
+    <row r="22" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A22" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B22" s="19">
         <v>2.25</v>
@@ -5988,9 +6002,9 @@
         <v>585</v>
       </c>
     </row>
-    <row r="23" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>166</v>
+    <row r="23" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B23" s="19">
         <v>2.5</v>
@@ -6284,9 +6298,9 @@
         <v>573</v>
       </c>
     </row>
-    <row r="24" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>166</v>
+    <row r="24" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B24" s="19">
         <v>2.75</v>
@@ -6580,9 +6594,9 @@
         <v>580</v>
       </c>
     </row>
-    <row r="25" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
-        <v>166</v>
+    <row r="25" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B25" s="19">
         <v>3</v>
@@ -6876,9 +6890,9 @@
         <v>581</v>
       </c>
     </row>
-    <row r="26" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
-        <v>166</v>
+    <row r="26" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B26" s="19">
         <v>3.25</v>
@@ -7172,9 +7186,9 @@
         <v>566</v>
       </c>
     </row>
-    <row r="27" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
-        <v>166</v>
+    <row r="27" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B27" s="19">
         <v>3.5</v>
@@ -7468,9 +7482,9 @@
         <v>573</v>
       </c>
     </row>
-    <row r="28" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
-        <v>166</v>
+    <row r="28" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A28" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B28" s="19">
         <v>3.75</v>
@@ -7764,9 +7778,9 @@
         <v>565</v>
       </c>
     </row>
-    <row r="29" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
-        <v>166</v>
+    <row r="29" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B29" s="19">
         <v>4</v>
@@ -8060,9 +8074,9 @@
         <v>610</v>
       </c>
     </row>
-    <row r="30" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
-        <v>166</v>
+    <row r="30" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A30" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B30" s="19">
         <v>4.25</v>
@@ -8356,9 +8370,9 @@
         <v>530</v>
       </c>
     </row>
-    <row r="31" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
-        <v>166</v>
+    <row r="31" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A31" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B31" s="19">
         <v>4.5</v>
@@ -8652,9 +8666,9 @@
         <v>581</v>
       </c>
     </row>
-    <row r="32" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>166</v>
+    <row r="32" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A32" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B32" s="19">
         <v>4.75</v>
@@ -8948,9 +8962,9 @@
         <v>580</v>
       </c>
     </row>
-    <row r="33" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
-        <v>166</v>
+    <row r="33" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A33" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B33" s="19">
         <v>5</v>
@@ -9244,9 +9258,9 @@
         <v>593</v>
       </c>
     </row>
-    <row r="34" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>166</v>
+    <row r="34" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B34" s="19">
         <v>5.25</v>
@@ -9540,9 +9554,9 @@
         <v>589</v>
       </c>
     </row>
-    <row r="35" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
-        <v>166</v>
+    <row r="35" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B35" s="19">
         <v>5.5</v>
@@ -9836,9 +9850,9 @@
         <v>543</v>
       </c>
     </row>
-    <row r="36" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="18" t="s">
-        <v>166</v>
+    <row r="36" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A36" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B36" s="19">
         <v>5.75</v>
@@ -10132,9 +10146,9 @@
         <v>568</v>
       </c>
     </row>
-    <row r="37" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="18" t="s">
-        <v>166</v>
+    <row r="37" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B37" s="19">
         <v>6</v>
@@ -10428,9 +10442,9 @@
         <v>542</v>
       </c>
     </row>
-    <row r="38" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
-        <v>166</v>
+    <row r="38" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A38" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B38" s="19">
         <v>6.25</v>
@@ -10724,9 +10738,9 @@
         <v>540</v>
       </c>
     </row>
-    <row r="39" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
-        <v>166</v>
+    <row r="39" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A39" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B39" s="19">
         <v>6.5</v>
@@ -11020,9 +11034,9 @@
         <v>557</v>
       </c>
     </row>
-    <row r="40" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="18" t="s">
-        <v>166</v>
+    <row r="40" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A40" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B40" s="19">
         <v>6.75</v>
@@ -11316,9 +11330,9 @@
         <v>540</v>
       </c>
     </row>
-    <row r="41" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="18" t="s">
-        <v>166</v>
+    <row r="41" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A41" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B41" s="19">
         <v>7</v>
@@ -11612,9 +11626,9 @@
         <v>556</v>
       </c>
     </row>
-    <row r="42" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
-        <v>166</v>
+    <row r="42" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A42" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B42" s="19">
         <v>7.25</v>
@@ -11908,9 +11922,9 @@
         <v>549</v>
       </c>
     </row>
-    <row r="43" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
-        <v>166</v>
+    <row r="43" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A43" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B43" s="19">
         <v>7.5</v>
@@ -12204,9 +12218,9 @@
         <v>566</v>
       </c>
     </row>
-    <row r="44" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
-        <v>166</v>
+    <row r="44" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A44" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B44" s="19">
         <v>7.75</v>
@@ -12500,9 +12514,9 @@
         <v>568</v>
       </c>
     </row>
-    <row r="45" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
-        <v>166</v>
+    <row r="45" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A45" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B45" s="19">
         <v>8</v>
@@ -12796,9 +12810,9 @@
         <v>576</v>
       </c>
     </row>
-    <row r="46" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="18" t="s">
-        <v>166</v>
+    <row r="46" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A46" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B46" s="19">
         <v>8.25</v>
@@ -13092,9 +13106,9 @@
         <v>574</v>
       </c>
     </row>
-    <row r="47" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="18" t="s">
-        <v>166</v>
+    <row r="47" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A47" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B47" s="19">
         <v>8.5</v>
@@ -13388,9 +13402,9 @@
         <v>554</v>
       </c>
     </row>
-    <row r="48" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="18" t="s">
-        <v>166</v>
+    <row r="48" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A48" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B48" s="19">
         <v>8.75</v>
@@ -13684,9 +13698,9 @@
         <v>570</v>
       </c>
     </row>
-    <row r="49" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="18" t="s">
-        <v>166</v>
+    <row r="49" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A49" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B49" s="19">
         <v>9</v>
@@ -13980,9 +13994,9 @@
         <v>574</v>
       </c>
     </row>
-    <row r="50" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="18" t="s">
-        <v>166</v>
+    <row r="50" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A50" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B50" s="19">
         <v>9.25</v>
@@ -14276,9 +14290,9 @@
         <v>557</v>
       </c>
     </row>
-    <row r="51" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="18" t="s">
-        <v>166</v>
+    <row r="51" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A51" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B51" s="19">
         <v>9.5</v>
@@ -14572,9 +14586,9 @@
         <v>578</v>
       </c>
     </row>
-    <row r="52" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="18" t="s">
-        <v>166</v>
+    <row r="52" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A52" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B52" s="19">
         <v>9.75</v>
@@ -14868,9 +14882,9 @@
         <v>570</v>
       </c>
     </row>
-    <row r="53" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="18" t="s">
-        <v>166</v>
+    <row r="53" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A53" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B53" s="19">
         <v>10</v>
@@ -15164,9 +15178,9 @@
         <v>572</v>
       </c>
     </row>
-    <row r="54" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="18" t="s">
-        <v>166</v>
+    <row r="54" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A54" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B54" s="19">
         <v>10.25</v>
@@ -15460,9 +15474,9 @@
         <v>585</v>
       </c>
     </row>
-    <row r="55" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
-        <v>166</v>
+    <row r="55" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A55" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B55" s="19">
         <v>10.5</v>
@@ -15756,9 +15770,9 @@
         <v>596</v>
       </c>
     </row>
-    <row r="56" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="s">
-        <v>166</v>
+    <row r="56" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A56" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B56" s="19">
         <v>10.75</v>
@@ -16052,9 +16066,9 @@
         <v>586</v>
       </c>
     </row>
-    <row r="57" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="18" t="s">
-        <v>166</v>
+    <row r="57" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A57" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B57" s="19">
         <v>11</v>
@@ -16348,9 +16362,9 @@
         <v>606</v>
       </c>
     </row>
-    <row r="58" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="18" t="s">
-        <v>166</v>
+    <row r="58" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A58" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B58" s="19">
         <v>11.25</v>
@@ -16644,9 +16658,9 @@
         <v>601</v>
       </c>
     </row>
-    <row r="59" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="18" t="s">
-        <v>166</v>
+    <row r="59" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A59" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B59" s="19">
         <v>11.5</v>
@@ -16940,9 +16954,9 @@
         <v>610</v>
       </c>
     </row>
-    <row r="60" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="18" t="s">
-        <v>166</v>
+    <row r="60" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A60" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B60" s="19">
         <v>11.75</v>
@@ -17236,9 +17250,9 @@
         <v>594</v>
       </c>
     </row>
-    <row r="61" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="18" t="s">
-        <v>166</v>
+    <row r="61" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A61" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B61" s="19">
         <v>12</v>
@@ -17532,9 +17546,9 @@
         <v>620</v>
       </c>
     </row>
-    <row r="62" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="18" t="s">
-        <v>166</v>
+    <row r="62" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A62" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B62" s="19">
         <v>12.25</v>
@@ -17828,9 +17842,9 @@
         <v>610</v>
       </c>
     </row>
-    <row r="63" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="18" t="s">
-        <v>166</v>
+    <row r="63" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A63" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B63" s="19">
         <v>12.5</v>
@@ -18124,9 +18138,9 @@
         <v>596</v>
       </c>
     </row>
-    <row r="64" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="18" t="s">
-        <v>166</v>
+    <row r="64" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A64" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B64" s="19">
         <v>12.75</v>
@@ -18420,9 +18434,9 @@
         <v>613</v>
       </c>
     </row>
-    <row r="65" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="18" t="s">
-        <v>166</v>
+    <row r="65" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A65" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B65" s="19">
         <v>13</v>
@@ -18716,9 +18730,9 @@
         <v>626</v>
       </c>
     </row>
-    <row r="66" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="18" t="s">
-        <v>166</v>
+    <row r="66" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A66" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B66" s="19">
         <v>13.25</v>
@@ -19012,9 +19026,9 @@
         <v>617</v>
       </c>
     </row>
-    <row r="67" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="18" t="s">
-        <v>166</v>
+    <row r="67" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A67" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B67" s="19">
         <v>13.5</v>
@@ -19308,9 +19322,9 @@
         <v>626</v>
       </c>
     </row>
-    <row r="68" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="18" t="s">
-        <v>166</v>
+    <row r="68" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A68" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B68" s="19">
         <v>13.75</v>
@@ -19604,9 +19618,9 @@
         <v>628</v>
       </c>
     </row>
-    <row r="69" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="18" t="s">
-        <v>166</v>
+    <row r="69" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A69" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B69" s="19">
         <v>14</v>
@@ -19900,9 +19914,9 @@
         <v>624</v>
       </c>
     </row>
-    <row r="70" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="18" t="s">
-        <v>166</v>
+    <row r="70" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A70" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B70" s="19">
         <v>14.25</v>
@@ -20196,9 +20210,9 @@
         <v>647</v>
       </c>
     </row>
-    <row r="71" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A71" s="18" t="s">
-        <v>166</v>
+    <row r="71" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A71" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B71" s="19">
         <v>14.5</v>
@@ -20492,9 +20506,9 @@
         <v>632</v>
       </c>
     </row>
-    <row r="72" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" s="18" t="s">
-        <v>166</v>
+    <row r="72" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A72" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B72" s="19">
         <v>14.75</v>
@@ -20788,9 +20802,9 @@
         <v>640</v>
       </c>
     </row>
-    <row r="73" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A73" s="18" t="s">
-        <v>166</v>
+    <row r="73" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A73" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B73" s="19">
         <v>15</v>
@@ -21084,9 +21098,9 @@
         <v>643</v>
       </c>
     </row>
-    <row r="74" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A74" s="18" t="s">
-        <v>166</v>
+    <row r="74" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A74" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B74" s="19">
         <v>15.25</v>
@@ -21380,9 +21394,9 @@
         <v>635</v>
       </c>
     </row>
-    <row r="75" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A75" s="18" t="s">
-        <v>166</v>
+    <row r="75" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A75" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B75" s="19">
         <v>15.5</v>
@@ -21676,9 +21690,9 @@
         <v>672</v>
       </c>
     </row>
-    <row r="76" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A76" s="18" t="s">
-        <v>166</v>
+    <row r="76" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A76" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B76" s="19">
         <v>15.75</v>
@@ -21972,9 +21986,9 @@
         <v>662</v>
       </c>
     </row>
-    <row r="77" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A77" s="18" t="s">
-        <v>166</v>
+    <row r="77" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A77" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B77" s="19">
         <v>16</v>
@@ -22268,9 +22282,9 @@
         <v>680</v>
       </c>
     </row>
-    <row r="78" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A78" s="18" t="s">
-        <v>166</v>
+    <row r="78" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A78" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B78" s="19">
         <v>16.25</v>
@@ -22564,9 +22578,9 @@
         <v>657</v>
       </c>
     </row>
-    <row r="79" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A79" s="18" t="s">
-        <v>166</v>
+    <row r="79" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A79" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B79" s="19">
         <v>16.5</v>
@@ -22860,9 +22874,9 @@
         <v>713</v>
       </c>
     </row>
-    <row r="80" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A80" s="18" t="s">
-        <v>166</v>
+    <row r="80" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A80" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B80" s="19">
         <v>16.75</v>
@@ -23156,9 +23170,9 @@
         <v>657</v>
       </c>
     </row>
-    <row r="81" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A81" s="18" t="s">
-        <v>166</v>
+    <row r="81" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A81" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B81" s="19">
         <v>17</v>
@@ -23452,9 +23466,9 @@
         <v>718</v>
       </c>
     </row>
-    <row r="82" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A82" s="18" t="s">
-        <v>166</v>
+    <row r="82" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A82" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B82" s="19">
         <v>17.25</v>
@@ -23748,9 +23762,9 @@
         <v>701</v>
       </c>
     </row>
-    <row r="83" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A83" s="18" t="s">
-        <v>166</v>
+    <row r="83" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A83" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B83" s="19">
         <v>17.5</v>
@@ -24044,9 +24058,9 @@
         <v>687</v>
       </c>
     </row>
-    <row r="84" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A84" s="18" t="s">
-        <v>166</v>
+    <row r="84" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A84" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B84" s="19">
         <v>17.75</v>
@@ -24340,9 +24354,9 @@
         <v>704</v>
       </c>
     </row>
-    <row r="85" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A85" s="18" t="s">
-        <v>166</v>
+    <row r="85" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A85" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B85" s="19">
         <v>18</v>
@@ -24636,9 +24650,9 @@
         <v>686</v>
       </c>
     </row>
-    <row r="86" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="18" t="s">
-        <v>166</v>
+    <row r="86" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A86" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B86" s="19">
         <v>18.25</v>
@@ -24932,9 +24946,9 @@
         <v>719</v>
       </c>
     </row>
-    <row r="87" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="18" t="s">
-        <v>166</v>
+    <row r="87" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A87" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B87" s="19">
         <v>18.5</v>
@@ -25228,9 +25242,9 @@
         <v>689</v>
       </c>
     </row>
-    <row r="88" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A88" s="18" t="s">
-        <v>166</v>
+    <row r="88" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A88" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B88" s="19">
         <v>18.75</v>
@@ -25524,9 +25538,9 @@
         <v>694</v>
       </c>
     </row>
-    <row r="89" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="18" t="s">
-        <v>166</v>
+    <row r="89" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A89" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B89" s="19">
         <v>19</v>
@@ -25820,9 +25834,9 @@
         <v>710</v>
       </c>
     </row>
-    <row r="90" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A90" s="18" t="s">
-        <v>166</v>
+    <row r="90" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A90" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B90" s="19">
         <v>19.25</v>
@@ -26116,9 +26130,9 @@
         <v>707</v>
       </c>
     </row>
-    <row r="91" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A91" s="18" t="s">
-        <v>166</v>
+    <row r="91" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A91" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B91" s="19">
         <v>19.5</v>
@@ -26412,9 +26426,9 @@
         <v>710</v>
       </c>
     </row>
-    <row r="92" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A92" s="18" t="s">
-        <v>166</v>
+    <row r="92" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A92" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B92" s="19">
         <v>19.75</v>
@@ -26708,9 +26722,9 @@
         <v>713</v>
       </c>
     </row>
-    <row r="93" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A93" s="18" t="s">
-        <v>166</v>
+    <row r="93" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A93" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B93" s="19">
         <v>20</v>
@@ -27004,9 +27018,9 @@
         <v>679</v>
       </c>
     </row>
-    <row r="94" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A94" s="18" t="s">
-        <v>166</v>
+    <row r="94" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A94" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B94" s="19">
         <v>20.25</v>
@@ -27300,9 +27314,9 @@
         <v>724</v>
       </c>
     </row>
-    <row r="95" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A95" s="18" t="s">
-        <v>166</v>
+    <row r="95" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A95" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B95" s="19">
         <v>20.5</v>
@@ -27596,9 +27610,9 @@
         <v>751</v>
       </c>
     </row>
-    <row r="96" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A96" s="18" t="s">
-        <v>166</v>
+    <row r="96" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A96" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B96" s="19">
         <v>20.75</v>
@@ -27892,9 +27906,9 @@
         <v>741</v>
       </c>
     </row>
-    <row r="97" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A97" s="18" t="s">
-        <v>166</v>
+    <row r="97" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A97" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B97" s="19">
         <v>21</v>
@@ -28188,9 +28202,9 @@
         <v>705</v>
       </c>
     </row>
-    <row r="98" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A98" s="18" t="s">
-        <v>166</v>
+    <row r="98" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A98" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B98" s="19">
         <v>21.25</v>
@@ -28484,9 +28498,9 @@
         <v>718</v>
       </c>
     </row>
-    <row r="99" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A99" s="18" t="s">
-        <v>166</v>
+    <row r="99" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A99" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B99" s="19">
         <v>21.5</v>
@@ -28780,9 +28794,9 @@
         <v>697</v>
       </c>
     </row>
-    <row r="100" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="18" t="s">
-        <v>166</v>
+    <row r="100" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A100" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B100" s="19">
         <v>21.75</v>
@@ -29076,9 +29090,9 @@
         <v>721</v>
       </c>
     </row>
-    <row r="101" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101" s="18" t="s">
-        <v>166</v>
+    <row r="101" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A101" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B101" s="19">
         <v>22</v>
@@ -29372,9 +29386,9 @@
         <v>705</v>
       </c>
     </row>
-    <row r="102" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A102" s="18" t="s">
-        <v>166</v>
+    <row r="102" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A102" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B102" s="19">
         <v>22.25</v>
@@ -29668,9 +29682,9 @@
         <v>750</v>
       </c>
     </row>
-    <row r="103" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103" s="18" t="s">
-        <v>166</v>
+    <row r="103" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A103" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B103" s="19">
         <v>22.5</v>
@@ -29964,9 +29978,9 @@
         <v>714</v>
       </c>
     </row>
-    <row r="104" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A104" s="18" t="s">
-        <v>166</v>
+    <row r="104" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A104" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B104" s="19">
         <v>22.75</v>
@@ -30260,9 +30274,9 @@
         <v>718</v>
       </c>
     </row>
-    <row r="105" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" s="18" t="s">
-        <v>166</v>
+    <row r="105" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A105" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B105" s="19">
         <v>23</v>
@@ -30556,9 +30570,9 @@
         <v>712</v>
       </c>
     </row>
-    <row r="106" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A106" s="18" t="s">
-        <v>166</v>
+    <row r="106" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A106" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B106" s="19">
         <v>23.25</v>
@@ -30852,9 +30866,9 @@
         <v>705</v>
       </c>
     </row>
-    <row r="107" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A107" s="18" t="s">
-        <v>166</v>
+    <row r="107" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A107" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B107" s="19">
         <v>23.5</v>
@@ -31148,9 +31162,9 @@
         <v>713</v>
       </c>
     </row>
-    <row r="108" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="18" t="s">
-        <v>166</v>
+    <row r="108" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A108" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B108" s="19">
         <v>23.75</v>
@@ -31444,9 +31458,9 @@
         <v>750</v>
       </c>
     </row>
-    <row r="109" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A109" s="18" t="s">
-        <v>166</v>
+    <row r="109" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A109" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B109" s="19">
         <v>24</v>
@@ -31740,9 +31754,9 @@
         <v>778</v>
       </c>
     </row>
-    <row r="110" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A110" s="18" t="s">
-        <v>166</v>
+    <row r="110" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A110" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B110" s="19">
         <v>24.25</v>
@@ -32036,9 +32050,9 @@
         <v>726</v>
       </c>
     </row>
-    <row r="111" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A111" s="18" t="s">
-        <v>166</v>
+    <row r="111" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A111" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B111" s="19">
         <v>24.5</v>
@@ -32332,9 +32346,9 @@
         <v>720</v>
       </c>
     </row>
-    <row r="112" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A112" s="18" t="s">
-        <v>166</v>
+    <row r="112" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A112" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B112" s="19">
         <v>24.75</v>
@@ -32628,9 +32642,9 @@
         <v>719</v>
       </c>
     </row>
-    <row r="113" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A113" s="18" t="s">
-        <v>166</v>
+    <row r="113" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A113" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B113" s="19">
         <v>25</v>
@@ -32924,9 +32938,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="114" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A114" s="18" t="s">
-        <v>166</v>
+    <row r="114" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A114" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B114" s="19">
         <v>25.25</v>
@@ -33220,9 +33234,9 @@
         <v>704</v>
       </c>
     </row>
-    <row r="115" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A115" s="18" t="s">
-        <v>166</v>
+    <row r="115" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A115" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B115" s="19">
         <v>25.5</v>
@@ -33516,9 +33530,9 @@
         <v>724</v>
       </c>
     </row>
-    <row r="116" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="18" t="s">
-        <v>166</v>
+    <row r="116" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A116" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B116" s="19">
         <v>25.75</v>
@@ -33812,9 +33826,9 @@
         <v>797</v>
       </c>
     </row>
-    <row r="117" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A117" s="18" t="s">
-        <v>166</v>
+    <row r="117" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A117" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B117" s="19">
         <v>26</v>
@@ -34108,9 +34122,9 @@
         <v>731</v>
       </c>
     </row>
-    <row r="118" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="18" t="s">
-        <v>166</v>
+    <row r="118" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A118" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B118" s="19">
         <v>26.25</v>
@@ -34404,9 +34418,9 @@
         <v>803</v>
       </c>
     </row>
-    <row r="119" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A119" s="18" t="s">
-        <v>166</v>
+    <row r="119" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A119" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B119" s="19">
         <v>26.5</v>
@@ -34700,9 +34714,9 @@
         <v>729</v>
       </c>
     </row>
-    <row r="120" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A120" s="18" t="s">
-        <v>166</v>
+    <row r="120" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A120" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B120" s="19">
         <v>26.75</v>
@@ -34996,9 +35010,9 @@
         <v>728</v>
       </c>
     </row>
-    <row r="121" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="18" t="s">
-        <v>166</v>
+    <row r="121" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A121" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B121" s="19">
         <v>27</v>
@@ -35292,9 +35306,9 @@
         <v>781</v>
       </c>
     </row>
-    <row r="122" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A122" s="18" t="s">
-        <v>166</v>
+    <row r="122" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A122" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B122" s="19">
         <v>27.25</v>
@@ -35588,9 +35602,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="123" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A123" s="18" t="s">
-        <v>166</v>
+    <row r="123" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A123" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B123" s="19">
         <v>27.5</v>
@@ -35884,9 +35898,9 @@
         <v>732</v>
       </c>
     </row>
-    <row r="124" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124" s="18" t="s">
-        <v>166</v>
+    <row r="124" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A124" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B124" s="19">
         <v>27.75</v>
@@ -36180,9 +36194,9 @@
         <v>725</v>
       </c>
     </row>
-    <row r="125" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A125" s="18" t="s">
-        <v>166</v>
+    <row r="125" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A125" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B125" s="19">
         <v>28</v>
@@ -36476,9 +36490,9 @@
         <v>709</v>
       </c>
     </row>
-    <row r="126" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A126" s="18" t="s">
-        <v>166</v>
+    <row r="126" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A126" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B126" s="19">
         <v>28.25</v>
@@ -36772,9 +36786,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="127" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A127" s="18" t="s">
-        <v>166</v>
+    <row r="127" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A127" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B127" s="19">
         <v>28.5</v>
@@ -37068,9 +37082,9 @@
         <v>728</v>
       </c>
     </row>
-    <row r="128" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="18" t="s">
-        <v>166</v>
+    <row r="128" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A128" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B128" s="19">
         <v>28.75</v>
@@ -37364,9 +37378,9 @@
         <v>722</v>
       </c>
     </row>
-    <row r="129" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A129" s="18" t="s">
-        <v>166</v>
+    <row r="129" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A129" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B129" s="19">
         <v>29</v>
@@ -37660,9 +37674,9 @@
         <v>731</v>
       </c>
     </row>
-    <row r="130" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A130" s="18" t="s">
-        <v>166</v>
+    <row r="130" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A130" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B130" s="19">
         <v>29.25</v>
@@ -37956,9 +37970,9 @@
         <v>730</v>
       </c>
     </row>
-    <row r="131" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A131" s="18" t="s">
-        <v>166</v>
+    <row r="131" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A131" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B131" s="19">
         <v>29.5</v>
@@ -38252,9 +38266,9 @@
         <v>800</v>
       </c>
     </row>
-    <row r="132" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A132" s="18" t="s">
-        <v>166</v>
+    <row r="132" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A132" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B132" s="19">
         <v>29.75</v>
@@ -38548,9 +38562,9 @@
         <v>755</v>
       </c>
     </row>
-    <row r="133" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A133" s="18" t="s">
-        <v>166</v>
+    <row r="133" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A133" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B133" s="19">
         <v>30</v>
@@ -38844,9 +38858,9 @@
         <v>720</v>
       </c>
     </row>
-    <row r="134" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A134" s="18" t="s">
-        <v>166</v>
+    <row r="134" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A134" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B134" s="19">
         <v>30.25</v>
@@ -39140,9 +39154,9 @@
         <v>718</v>
       </c>
     </row>
-    <row r="135" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A135" s="18" t="s">
-        <v>166</v>
+    <row r="135" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A135" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B135" s="19">
         <v>30.5</v>
@@ -39436,9 +39450,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="136" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A136" s="18" t="s">
-        <v>166</v>
+    <row r="136" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A136" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B136" s="19">
         <v>30.75</v>
@@ -39732,9 +39746,9 @@
         <v>715</v>
       </c>
     </row>
-    <row r="137" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A137" s="18" t="s">
-        <v>166</v>
+    <row r="137" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A137" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B137" s="19">
         <v>31</v>
@@ -40028,9 +40042,9 @@
         <v>720</v>
       </c>
     </row>
-    <row r="138" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A138" s="18" t="s">
-        <v>166</v>
+    <row r="138" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A138" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B138" s="19">
         <v>31.25</v>
@@ -40324,9 +40338,9 @@
         <v>727</v>
       </c>
     </row>
-    <row r="139" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A139" s="18" t="s">
-        <v>166</v>
+    <row r="139" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A139" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B139" s="19">
         <v>31.5</v>
@@ -40620,9 +40634,9 @@
         <v>722</v>
       </c>
     </row>
-    <row r="140" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A140" s="18" t="s">
-        <v>166</v>
+    <row r="140" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A140" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B140" s="19">
         <v>31.75</v>
@@ -40916,9 +40930,9 @@
         <v>748</v>
       </c>
     </row>
-    <row r="141" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A141" s="18" t="s">
-        <v>166</v>
+    <row r="141" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A141" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B141" s="19">
         <v>32</v>
@@ -41212,9 +41226,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="142" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A142" s="18" t="s">
-        <v>166</v>
+    <row r="142" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A142" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B142" s="19">
         <v>32.25</v>
@@ -41508,9 +41522,9 @@
         <v>744</v>
       </c>
     </row>
-    <row r="143" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A143" s="18" t="s">
-        <v>166</v>
+    <row r="143" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A143" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B143" s="19">
         <v>32.5</v>
@@ -41804,9 +41818,9 @@
         <v>717</v>
       </c>
     </row>
-    <row r="144" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A144" s="18" t="s">
-        <v>166</v>
+    <row r="144" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A144" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B144" s="19">
         <v>32.75</v>
@@ -42100,9 +42114,9 @@
         <v>724</v>
       </c>
     </row>
-    <row r="145" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A145" s="18" t="s">
-        <v>166</v>
+    <row r="145" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A145" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B145" s="19">
         <v>33</v>
@@ -42396,9 +42410,9 @@
         <v>747</v>
       </c>
     </row>
-    <row r="146" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A146" s="18" t="s">
-        <v>166</v>
+    <row r="146" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A146" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B146" s="19">
         <v>33.25</v>
@@ -42692,9 +42706,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="147" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A147" s="18" t="s">
-        <v>166</v>
+    <row r="147" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A147" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B147" s="19">
         <v>33.5</v>
@@ -42988,9 +43002,9 @@
         <v>741</v>
       </c>
     </row>
-    <row r="148" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A148" s="18" t="s">
-        <v>166</v>
+    <row r="148" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A148" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B148" s="19">
         <v>33.75</v>
@@ -43284,9 +43298,9 @@
         <v>756</v>
       </c>
     </row>
-    <row r="149" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A149" s="18" t="s">
-        <v>166</v>
+    <row r="149" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A149" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B149" s="19">
         <v>34</v>
@@ -43580,9 +43594,9 @@
         <v>738</v>
       </c>
     </row>
-    <row r="150" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A150" s="18" t="s">
-        <v>166</v>
+    <row r="150" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A150" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B150" s="19">
         <v>34.25</v>
@@ -43876,9 +43890,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="151" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A151" s="18" t="s">
-        <v>166</v>
+    <row r="151" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A151" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B151" s="19">
         <v>34.5</v>
@@ -44172,9 +44186,9 @@
         <v>722</v>
       </c>
     </row>
-    <row r="152" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A152" s="18" t="s">
-        <v>166</v>
+    <row r="152" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A152" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B152" s="19">
         <v>34.75</v>
@@ -44468,9 +44482,9 @@
         <v>739</v>
       </c>
     </row>
-    <row r="153" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A153" s="18" t="s">
-        <v>166</v>
+    <row r="153" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A153" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B153" s="19">
         <v>35</v>
@@ -44764,9 +44778,9 @@
         <v>741</v>
       </c>
     </row>
-    <row r="154" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A154" s="18" t="s">
-        <v>166</v>
+    <row r="154" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A154" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B154" s="19">
         <v>35.25</v>
@@ -45060,9 +45074,9 @@
         <v>724</v>
       </c>
     </row>
-    <row r="155" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A155" s="18" t="s">
-        <v>166</v>
+    <row r="155" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A155" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B155" s="19">
         <v>35.5</v>
@@ -45356,9 +45370,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="156" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A156" s="18" t="s">
-        <v>166</v>
+    <row r="156" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A156" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B156" s="19">
         <v>35.75</v>
@@ -45652,9 +45666,9 @@
         <v>731</v>
       </c>
     </row>
-    <row r="157" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A157" s="18" t="s">
-        <v>166</v>
+    <row r="157" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A157" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B157" s="19">
         <v>36</v>
@@ -45948,9 +45962,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="158" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A158" s="18" t="s">
-        <v>166</v>
+    <row r="158" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A158" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B158" s="19">
         <v>36.25</v>
@@ -46244,9 +46258,9 @@
         <v>746</v>
       </c>
     </row>
-    <row r="159" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A159" s="18" t="s">
-        <v>166</v>
+    <row r="159" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A159" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B159" s="19">
         <v>36.5</v>
@@ -46540,9 +46554,9 @@
         <v>747</v>
       </c>
     </row>
-    <row r="160" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A160" s="18" t="s">
-        <v>166</v>
+    <row r="160" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A160" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B160" s="19">
         <v>36.75</v>
@@ -46836,9 +46850,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="161" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A161" s="18" t="s">
-        <v>166</v>
+    <row r="161" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A161" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B161" s="19">
         <v>37</v>
@@ -47132,9 +47146,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="162" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A162" s="18" t="s">
-        <v>166</v>
+    <row r="162" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A162" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B162" s="19">
         <v>37.25</v>
@@ -47428,9 +47442,9 @@
         <v>721</v>
       </c>
     </row>
-    <row r="163" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A163" s="18" t="s">
-        <v>166</v>
+    <row r="163" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A163" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B163" s="19">
         <v>37.5</v>
@@ -47724,9 +47738,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="164" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A164" s="18" t="s">
-        <v>166</v>
+    <row r="164" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A164" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B164" s="19">
         <v>37.75</v>
@@ -48020,9 +48034,9 @@
         <v>737</v>
       </c>
     </row>
-    <row r="165" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A165" s="18" t="s">
-        <v>166</v>
+    <row r="165" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A165" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B165" s="19">
         <v>38</v>
@@ -48316,9 +48330,9 @@
         <v>752</v>
       </c>
     </row>
-    <row r="166" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A166" s="18" t="s">
-        <v>166</v>
+    <row r="166" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A166" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B166" s="19">
         <v>38.25</v>
@@ -48612,9 +48626,9 @@
         <v>729</v>
       </c>
     </row>
-    <row r="167" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A167" s="18" t="s">
-        <v>166</v>
+    <row r="167" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A167" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B167" s="19">
         <v>38.5</v>
@@ -48908,9 +48922,9 @@
         <v>723</v>
       </c>
     </row>
-    <row r="168" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A168" s="18" t="s">
-        <v>166</v>
+    <row r="168" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A168" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B168" s="19">
         <v>38.75</v>
@@ -49204,9 +49218,9 @@
         <v>724</v>
       </c>
     </row>
-    <row r="169" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A169" s="18" t="s">
-        <v>166</v>
+    <row r="169" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A169" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B169" s="19">
         <v>39</v>
@@ -49500,9 +49514,9 @@
         <v>725</v>
       </c>
     </row>
-    <row r="170" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A170" s="18" t="s">
-        <v>166</v>
+    <row r="170" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A170" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B170" s="19">
         <v>39.25</v>
@@ -49796,9 +49810,9 @@
         <v>718</v>
       </c>
     </row>
-    <row r="171" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A171" s="18" t="s">
-        <v>166</v>
+    <row r="171" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A171" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B171" s="19">
         <v>39.5</v>
@@ -50092,9 +50106,9 @@
         <v>726</v>
       </c>
     </row>
-    <row r="172" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A172" s="18" t="s">
-        <v>166</v>
+    <row r="172" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A172" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B172" s="19">
         <v>39.75</v>
@@ -50388,9 +50402,9 @@
         <v>731</v>
       </c>
     </row>
-    <row r="173" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A173" s="18" t="s">
-        <v>166</v>
+    <row r="173" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A173" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B173" s="19">
         <v>40</v>
@@ -50684,9 +50698,9 @@
         <v>720</v>
       </c>
     </row>
-    <row r="174" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A174" s="18" t="s">
-        <v>166</v>
+    <row r="174" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A174" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B174" s="19">
         <v>40.25</v>
@@ -50980,9 +50994,9 @@
         <v>745</v>
       </c>
     </row>
-    <row r="175" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A175" s="18" t="s">
-        <v>166</v>
+    <row r="175" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A175" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B175" s="19">
         <v>40.5</v>
@@ -51276,9 +51290,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="176" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A176" s="18" t="s">
-        <v>166</v>
+    <row r="176" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A176" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B176" s="19">
         <v>40.75</v>
@@ -51572,9 +51586,9 @@
         <v>726</v>
       </c>
     </row>
-    <row r="177" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A177" s="18" t="s">
-        <v>166</v>
+    <row r="177" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A177" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B177" s="19">
         <v>41</v>
@@ -51868,9 +51882,9 @@
         <v>717</v>
       </c>
     </row>
-    <row r="178" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A178" s="18" t="s">
-        <v>166</v>
+    <row r="178" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A178" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B178" s="19">
         <v>41.25</v>
@@ -52164,9 +52178,9 @@
         <v>732</v>
       </c>
     </row>
-    <row r="179" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A179" s="18" t="s">
-        <v>166</v>
+    <row r="179" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A179" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B179" s="19">
         <v>41.5</v>
@@ -52460,9 +52474,9 @@
         <v>754</v>
       </c>
     </row>
-    <row r="180" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A180" s="18" t="s">
-        <v>166</v>
+    <row r="180" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A180" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B180" s="19">
         <v>41.75</v>
@@ -52756,9 +52770,9 @@
         <v>721</v>
       </c>
     </row>
-    <row r="181" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A181" s="18" t="s">
-        <v>166</v>
+    <row r="181" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A181" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B181" s="19">
         <v>42</v>
@@ -53052,9 +53066,9 @@
         <v>751</v>
       </c>
     </row>
-    <row r="182" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A182" s="18" t="s">
-        <v>166</v>
+    <row r="182" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A182" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B182" s="19">
         <v>42.25</v>
@@ -53348,9 +53362,9 @@
         <v>735</v>
       </c>
     </row>
-    <row r="183" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A183" s="18" t="s">
-        <v>166</v>
+    <row r="183" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A183" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B183" s="19">
         <v>42.5</v>
@@ -53644,9 +53658,9 @@
         <v>725</v>
       </c>
     </row>
-    <row r="184" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A184" s="18" t="s">
-        <v>166</v>
+    <row r="184" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A184" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B184" s="19">
         <v>42.75</v>
@@ -53940,9 +53954,9 @@
         <v>727</v>
       </c>
     </row>
-    <row r="185" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A185" s="18" t="s">
-        <v>166</v>
+    <row r="185" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A185" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B185" s="19">
         <v>43</v>
@@ -54236,9 +54250,9 @@
         <v>754</v>
       </c>
     </row>
-    <row r="186" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A186" s="18" t="s">
-        <v>166</v>
+    <row r="186" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A186" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B186" s="19">
         <v>43.25</v>
@@ -54532,9 +54546,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="187" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A187" s="18" t="s">
-        <v>166</v>
+    <row r="187" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A187" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B187" s="19">
         <v>43.5</v>
@@ -54828,9 +54842,9 @@
         <v>729</v>
       </c>
     </row>
-    <row r="188" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A188" s="18" t="s">
-        <v>166</v>
+    <row r="188" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A188" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B188" s="19">
         <v>43.75</v>
@@ -55124,9 +55138,9 @@
         <v>719</v>
       </c>
     </row>
-    <row r="189" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A189" s="18" t="s">
-        <v>166</v>
+    <row r="189" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A189" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B189" s="19">
         <v>44</v>
@@ -55420,9 +55434,9 @@
         <v>727</v>
       </c>
     </row>
-    <row r="190" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A190" s="18" t="s">
-        <v>166</v>
+    <row r="190" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A190" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B190" s="19">
         <v>44.25</v>
@@ -55716,9 +55730,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="191" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A191" s="18" t="s">
-        <v>166</v>
+    <row r="191" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A191" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B191" s="19">
         <v>44.5</v>
@@ -56012,9 +56026,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="192" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A192" s="18" t="s">
-        <v>166</v>
+    <row r="192" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A192" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B192" s="19">
         <v>44.75</v>
@@ -56308,9 +56322,9 @@
         <v>724</v>
       </c>
     </row>
-    <row r="193" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A193" s="18" t="s">
-        <v>166</v>
+    <row r="193" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A193" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B193" s="19">
         <v>45</v>
@@ -56604,9 +56618,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="194" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A194" s="18" t="s">
-        <v>166</v>
+    <row r="194" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A194" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B194" s="19">
         <v>45.25</v>
@@ -56900,9 +56914,9 @@
         <v>730</v>
       </c>
     </row>
-    <row r="195" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A195" s="18" t="s">
-        <v>166</v>
+    <row r="195" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A195" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B195" s="19">
         <v>45.5</v>
@@ -57196,9 +57210,9 @@
         <v>732</v>
       </c>
     </row>
-    <row r="196" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A196" s="18" t="s">
-        <v>166</v>
+    <row r="196" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A196" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B196" s="19">
         <v>45.75</v>
@@ -57492,9 +57506,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="197" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A197" s="18" t="s">
-        <v>166</v>
+    <row r="197" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A197" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B197" s="19">
         <v>46</v>
@@ -57788,9 +57802,9 @@
         <v>716</v>
       </c>
     </row>
-    <row r="198" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A198" s="18" t="s">
-        <v>166</v>
+    <row r="198" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A198" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B198" s="19">
         <v>46.25</v>
@@ -58084,9 +58098,9 @@
         <v>732</v>
       </c>
     </row>
-    <row r="199" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A199" s="18" t="s">
-        <v>166</v>
+    <row r="199" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A199" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B199" s="19">
         <v>46.5</v>
@@ -58380,9 +58394,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="200" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A200" s="18" t="s">
-        <v>166</v>
+    <row r="200" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A200" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B200" s="19">
         <v>46.75</v>
@@ -58676,9 +58690,9 @@
         <v>753</v>
       </c>
     </row>
-    <row r="201" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A201" s="18" t="s">
-        <v>166</v>
+    <row r="201" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A201" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B201" s="19">
         <v>47</v>
@@ -58972,9 +58986,9 @@
         <v>748</v>
       </c>
     </row>
-    <row r="202" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A202" s="18" t="s">
-        <v>166</v>
+    <row r="202" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A202" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B202" s="19">
         <v>47.25</v>
@@ -59268,9 +59282,9 @@
         <v>762</v>
       </c>
     </row>
-    <row r="203" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A203" s="18" t="s">
-        <v>166</v>
+    <row r="203" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A203" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B203" s="19">
         <v>47.5</v>
@@ -59564,9 +59578,9 @@
         <v>761</v>
       </c>
     </row>
-    <row r="204" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A204" s="18" t="s">
-        <v>166</v>
+    <row r="204" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A204" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B204" s="19">
         <v>47.75</v>
@@ -59860,9 +59874,9 @@
         <v>726</v>
       </c>
     </row>
-    <row r="205" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A205" s="18" t="s">
-        <v>166</v>
+    <row r="205" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A205" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B205" s="19">
         <v>48</v>
@@ -60156,9 +60170,9 @@
         <v>737</v>
       </c>
     </row>
-    <row r="206" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A206" s="18" t="s">
-        <v>166</v>
+    <row r="206" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A206" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B206" s="19">
         <v>48.25</v>
@@ -60452,9 +60466,9 @@
         <v>755</v>
       </c>
     </row>
-    <row r="207" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A207" s="18" t="s">
-        <v>166</v>
+    <row r="207" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A207" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B207" s="19">
         <v>48.5</v>
@@ -60748,9 +60762,9 @@
         <v>728</v>
       </c>
     </row>
-    <row r="208" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A208" s="18" t="s">
-        <v>166</v>
+    <row r="208" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A208" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B208" s="19">
         <v>48.75</v>
@@ -61044,9 +61058,9 @@
         <v>755</v>
       </c>
     </row>
-    <row r="209" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A209" s="18" t="s">
-        <v>166</v>
+    <row r="209" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A209" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B209" s="19">
         <v>49</v>
@@ -61340,9 +61354,9 @@
         <v>713</v>
       </c>
     </row>
-    <row r="210" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A210" s="18" t="s">
-        <v>166</v>
+    <row r="210" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A210" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B210" s="19">
         <v>49.25</v>
@@ -61636,9 +61650,9 @@
         <v>741</v>
       </c>
     </row>
-    <row r="211" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A211" s="18" t="s">
-        <v>166</v>
+    <row r="211" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A211" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B211" s="19">
         <v>49.5</v>
@@ -61932,9 +61946,9 @@
         <v>738</v>
       </c>
     </row>
-    <row r="212" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A212" s="18" t="s">
-        <v>166</v>
+    <row r="212" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A212" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B212" s="19">
         <v>49.75</v>
@@ -62228,9 +62242,9 @@
         <v>733</v>
       </c>
     </row>
-    <row r="213" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A213" s="18" t="s">
-        <v>166</v>
+    <row r="213" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A213" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B213" s="19">
         <v>50</v>
@@ -62524,9 +62538,9 @@
         <v>744</v>
       </c>
     </row>
-    <row r="214" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A214" s="18" t="s">
-        <v>166</v>
+    <row r="214" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A214" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B214" s="19">
         <v>50.25</v>
@@ -62820,9 +62834,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="215" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A215" s="18" t="s">
-        <v>166</v>
+    <row r="215" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A215" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B215" s="19">
         <v>50.5</v>
@@ -63116,9 +63130,9 @@
         <v>729</v>
       </c>
     </row>
-    <row r="216" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A216" s="18" t="s">
-        <v>166</v>
+    <row r="216" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A216" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B216" s="19">
         <v>50.75</v>
@@ -63412,9 +63426,9 @@
         <v>720</v>
       </c>
     </row>
-    <row r="217" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A217" s="18" t="s">
-        <v>166</v>
+    <row r="217" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A217" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B217" s="19">
         <v>51</v>
@@ -63708,9 +63722,9 @@
         <v>726</v>
       </c>
     </row>
-    <row r="218" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A218" s="18" t="s">
-        <v>166</v>
+    <row r="218" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A218" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B218" s="19">
         <v>51.25</v>
@@ -64004,9 +64018,9 @@
         <v>713</v>
       </c>
     </row>
-    <row r="219" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A219" s="18" t="s">
-        <v>166</v>
+    <row r="219" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A219" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B219" s="19">
         <v>51.5</v>
@@ -64300,9 +64314,9 @@
         <v>751</v>
       </c>
     </row>
-    <row r="220" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A220" s="18" t="s">
-        <v>166</v>
+    <row r="220" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A220" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B220" s="19">
         <v>51.75</v>
@@ -64596,9 +64610,9 @@
         <v>725</v>
       </c>
     </row>
-    <row r="221" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A221" s="18" t="s">
-        <v>166</v>
+    <row r="221" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A221" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B221" s="19">
         <v>52</v>
@@ -64892,9 +64906,9 @@
         <v>735</v>
       </c>
     </row>
-    <row r="222" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A222" s="18" t="s">
-        <v>166</v>
+    <row r="222" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A222" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B222" s="19">
         <v>52.25</v>
@@ -65188,9 +65202,9 @@
         <v>728</v>
       </c>
     </row>
-    <row r="223" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A223" s="18" t="s">
-        <v>166</v>
+    <row r="223" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A223" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B223" s="19">
         <v>52.5</v>
@@ -65484,9 +65498,9 @@
         <v>727</v>
       </c>
     </row>
-    <row r="224" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A224" s="18" t="s">
-        <v>166</v>
+    <row r="224" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A224" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B224" s="19">
         <v>52.75</v>
@@ -65780,9 +65794,9 @@
         <v>730</v>
       </c>
     </row>
-    <row r="225" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A225" s="18" t="s">
-        <v>166</v>
+    <row r="225" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A225" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B225" s="19">
         <v>53</v>
@@ -66076,9 +66090,9 @@
         <v>746</v>
       </c>
     </row>
-    <row r="226" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A226" s="18" t="s">
-        <v>166</v>
+    <row r="226" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A226" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B226" s="19">
         <v>53.25</v>
@@ -66372,9 +66386,9 @@
         <v>728</v>
       </c>
     </row>
-    <row r="227" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A227" s="18" t="s">
-        <v>166</v>
+    <row r="227" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A227" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B227" s="19">
         <v>53.5</v>
@@ -66668,9 +66682,9 @@
         <v>735</v>
       </c>
     </row>
-    <row r="228" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A228" s="18" t="s">
-        <v>166</v>
+    <row r="228" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A228" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B228" s="19">
         <v>53.75</v>
@@ -66964,9 +66978,9 @@
         <v>754</v>
       </c>
     </row>
-    <row r="229" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A229" s="18" t="s">
-        <v>166</v>
+    <row r="229" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A229" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B229" s="19">
         <v>54</v>
@@ -67260,9 +67274,9 @@
         <v>729</v>
       </c>
     </row>
-    <row r="230" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A230" s="18" t="s">
-        <v>166</v>
+    <row r="230" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A230" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B230" s="19">
         <v>54.25</v>
@@ -67556,9 +67570,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="231" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A231" s="18" t="s">
-        <v>166</v>
+    <row r="231" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A231" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B231" s="19">
         <v>54.5</v>
@@ -67852,9 +67866,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="232" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A232" s="18" t="s">
-        <v>166</v>
+    <row r="232" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A232" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B232" s="19">
         <v>54.75</v>
@@ -68148,9 +68162,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="233" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A233" s="18" t="s">
-        <v>166</v>
+    <row r="233" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A233" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B233" s="19">
         <v>55</v>
@@ -68444,9 +68458,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="234" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A234" s="18" t="s">
-        <v>166</v>
+    <row r="234" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A234" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B234" s="19">
         <v>55.25</v>
@@ -68740,9 +68754,9 @@
         <v>735</v>
       </c>
     </row>
-    <row r="235" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A235" s="18" t="s">
-        <v>166</v>
+    <row r="235" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A235" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B235" s="19">
         <v>55.5</v>
@@ -69036,9 +69050,9 @@
         <v>744</v>
       </c>
     </row>
-    <row r="236" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A236" s="18" t="s">
-        <v>166</v>
+    <row r="236" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A236" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B236" s="19">
         <v>55.75</v>
@@ -69332,9 +69346,9 @@
         <v>739</v>
       </c>
     </row>
-    <row r="237" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A237" s="18" t="s">
-        <v>166</v>
+    <row r="237" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A237" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B237" s="19">
         <v>56</v>
@@ -69628,9 +69642,9 @@
         <v>724</v>
       </c>
     </row>
-    <row r="238" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A238" s="18" t="s">
-        <v>166</v>
+    <row r="238" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A238" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B238" s="19">
         <v>56.25</v>
@@ -69924,9 +69938,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="239" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A239" s="18" t="s">
-        <v>166</v>
+    <row r="239" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A239" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B239" s="19">
         <v>56.5</v>
@@ -70220,9 +70234,9 @@
         <v>694</v>
       </c>
     </row>
-    <row r="240" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A240" s="18" t="s">
-        <v>166</v>
+    <row r="240" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A240" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B240" s="19">
         <v>56.75</v>
@@ -70516,9 +70530,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="241" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A241" s="18" t="s">
-        <v>166</v>
+    <row r="241" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A241" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B241" s="19">
         <v>57</v>
@@ -70812,9 +70826,9 @@
         <v>733</v>
       </c>
     </row>
-    <row r="242" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A242" s="18" t="s">
-        <v>166</v>
+    <row r="242" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A242" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B242" s="19">
         <v>57.25</v>
@@ -71108,9 +71122,9 @@
         <v>742</v>
       </c>
     </row>
-    <row r="243" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A243" s="18" t="s">
-        <v>166</v>
+    <row r="243" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A243" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B243" s="19">
         <v>57.5</v>
@@ -71404,9 +71418,9 @@
         <v>738</v>
       </c>
     </row>
-    <row r="244" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A244" s="18" t="s">
-        <v>166</v>
+    <row r="244" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A244" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B244" s="19">
         <v>57.75</v>
@@ -71700,9 +71714,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="245" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A245" s="18" t="s">
-        <v>166</v>
+    <row r="245" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A245" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B245" s="19">
         <v>58</v>
@@ -71996,9 +72010,9 @@
         <v>749</v>
       </c>
     </row>
-    <row r="246" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A246" s="18" t="s">
-        <v>166</v>
+    <row r="246" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A246" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B246" s="19">
         <v>58.25</v>
@@ -72292,9 +72306,9 @@
         <v>738</v>
       </c>
     </row>
-    <row r="247" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A247" s="18" t="s">
-        <v>166</v>
+    <row r="247" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A247" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B247" s="19">
         <v>58.5</v>
@@ -72588,9 +72602,9 @@
         <v>750</v>
       </c>
     </row>
-    <row r="248" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A248" s="18" t="s">
-        <v>166</v>
+    <row r="248" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A248" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B248" s="19">
         <v>58.75</v>
@@ -72884,9 +72898,9 @@
         <v>746</v>
       </c>
     </row>
-    <row r="249" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A249" s="18" t="s">
-        <v>166</v>
+    <row r="249" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A249" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B249" s="19">
         <v>59</v>
@@ -73180,9 +73194,9 @@
         <v>739</v>
       </c>
     </row>
-    <row r="250" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A250" s="18" t="s">
-        <v>166</v>
+    <row r="250" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A250" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B250" s="19">
         <v>59.25</v>
@@ -73476,9 +73490,9 @@
         <v>741</v>
       </c>
     </row>
-    <row r="251" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A251" s="18" t="s">
-        <v>166</v>
+    <row r="251" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A251" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B251" s="19">
         <v>59.5</v>
@@ -73772,9 +73786,9 @@
         <v>730</v>
       </c>
     </row>
-    <row r="252" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A252" s="18" t="s">
-        <v>166</v>
+    <row r="252" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A252" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B252" s="19">
         <v>59.75</v>
@@ -74068,9 +74082,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="253" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A253" s="18" t="s">
-        <v>166</v>
+    <row r="253" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A253" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B253" s="19">
         <v>60</v>
@@ -74364,9 +74378,9 @@
         <v>760</v>
       </c>
     </row>
-    <row r="254" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A254" s="18" t="s">
-        <v>166</v>
+    <row r="254" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A254" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B254" s="19">
         <v>60.25</v>
@@ -74660,9 +74674,9 @@
         <v>696</v>
       </c>
     </row>
-    <row r="255" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A255" s="18" t="s">
-        <v>166</v>
+    <row r="255" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A255" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B255" s="19">
         <v>60.5</v>
@@ -74956,9 +74970,9 @@
         <v>720</v>
       </c>
     </row>
-    <row r="256" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A256" s="18" t="s">
-        <v>166</v>
+    <row r="256" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A256" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B256" s="19">
         <v>60.75</v>
@@ -75252,9 +75266,9 @@
         <v>745</v>
       </c>
     </row>
-    <row r="257" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A257" s="18" t="s">
-        <v>166</v>
+    <row r="257" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A257" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B257" s="19">
         <v>61</v>
@@ -75548,9 +75562,9 @@
         <v>722</v>
       </c>
     </row>
-    <row r="258" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A258" s="18" t="s">
-        <v>166</v>
+    <row r="258" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A258" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B258" s="19">
         <v>61.25</v>
@@ -75844,9 +75858,9 @@
         <v>780</v>
       </c>
     </row>
-    <row r="259" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A259" s="18" t="s">
-        <v>166</v>
+    <row r="259" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A259" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B259" s="19">
         <v>61.5</v>
@@ -76140,9 +76154,9 @@
         <v>731</v>
       </c>
     </row>
-    <row r="260" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A260" s="18" t="s">
-        <v>166</v>
+    <row r="260" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A260" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B260" s="19">
         <v>61.75</v>
@@ -76436,9 +76450,9 @@
         <v>716</v>
       </c>
     </row>
-    <row r="261" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A261" s="18" t="s">
-        <v>166</v>
+    <row r="261" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A261" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B261" s="19">
         <v>62</v>
@@ -76732,9 +76746,9 @@
         <v>732</v>
       </c>
     </row>
-    <row r="262" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A262" s="18" t="s">
-        <v>166</v>
+    <row r="262" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A262" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B262" s="19">
         <v>62.25</v>
@@ -77028,9 +77042,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="263" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A263" s="18" t="s">
-        <v>166</v>
+    <row r="263" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A263" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B263" s="19">
         <v>62.5</v>
@@ -77324,9 +77338,9 @@
         <v>709</v>
       </c>
     </row>
-    <row r="264" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A264" s="18" t="s">
-        <v>166</v>
+    <row r="264" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A264" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B264" s="19">
         <v>62.75</v>
@@ -77620,9 +77634,9 @@
         <v>718</v>
       </c>
     </row>
-    <row r="265" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A265" s="18" t="s">
-        <v>166</v>
+    <row r="265" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A265" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B265" s="19">
         <v>63</v>
@@ -77916,9 +77930,9 @@
         <v>719</v>
       </c>
     </row>
-    <row r="266" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A266" s="18" t="s">
-        <v>166</v>
+    <row r="266" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A266" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B266" s="19">
         <v>63.25</v>
@@ -78212,9 +78226,9 @@
         <v>735</v>
       </c>
     </row>
-    <row r="267" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A267" s="18" t="s">
-        <v>166</v>
+    <row r="267" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A267" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B267" s="19">
         <v>63.5</v>
@@ -78508,9 +78522,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="268" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A268" s="18" t="s">
-        <v>166</v>
+    <row r="268" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A268" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B268" s="19">
         <v>63.75</v>
@@ -78804,9 +78818,9 @@
         <v>721</v>
       </c>
     </row>
-    <row r="269" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A269" s="18" t="s">
-        <v>166</v>
+    <row r="269" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A269" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B269" s="19">
         <v>64</v>
@@ -79100,9 +79114,9 @@
         <v>715</v>
       </c>
     </row>
-    <row r="270" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A270" s="18" t="s">
-        <v>166</v>
+    <row r="270" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A270" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B270" s="19">
         <v>64.25</v>
@@ -79396,9 +79410,9 @@
         <v>741</v>
       </c>
     </row>
-    <row r="271" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A271" s="18" t="s">
-        <v>166</v>
+    <row r="271" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A271" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B271" s="19">
         <v>64.5</v>
@@ -79692,9 +79706,9 @@
         <v>723</v>
       </c>
     </row>
-    <row r="272" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A272" s="18" t="s">
-        <v>166</v>
+    <row r="272" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A272" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B272" s="19">
         <v>64.75</v>
@@ -79988,9 +80002,9 @@
         <v>714</v>
       </c>
     </row>
-    <row r="273" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A273" s="18" t="s">
-        <v>166</v>
+    <row r="273" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A273" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B273" s="19">
         <v>65</v>
@@ -80284,9 +80298,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="274" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A274" s="18" t="s">
-        <v>166</v>
+    <row r="274" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A274" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B274" s="19">
         <v>65.25</v>
@@ -80580,9 +80594,9 @@
         <v>715</v>
       </c>
     </row>
-    <row r="275" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A275" s="18" t="s">
-        <v>166</v>
+    <row r="275" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A275" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B275" s="19">
         <v>65.5</v>
@@ -80876,9 +80890,9 @@
         <v>713</v>
       </c>
     </row>
-    <row r="276" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A276" s="18" t="s">
-        <v>166</v>
+    <row r="276" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A276" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B276" s="19">
         <v>65.75</v>
@@ -81172,9 +81186,9 @@
         <v>739</v>
       </c>
     </row>
-    <row r="277" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A277" s="18" t="s">
-        <v>166</v>
+    <row r="277" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A277" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B277" s="19">
         <v>66</v>
@@ -81468,9 +81482,9 @@
         <v>697</v>
       </c>
     </row>
-    <row r="278" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A278" s="18" t="s">
-        <v>166</v>
+    <row r="278" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A278" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B278" s="19">
         <v>66.25</v>
@@ -81764,9 +81778,9 @@
         <v>733</v>
       </c>
     </row>
-    <row r="279" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A279" s="18" t="s">
-        <v>166</v>
+    <row r="279" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A279" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B279" s="19">
         <v>66.5</v>
@@ -82060,9 +82074,9 @@
         <v>702</v>
       </c>
     </row>
-    <row r="280" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A280" s="18" t="s">
-        <v>166</v>
+    <row r="280" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A280" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B280" s="19">
         <v>66.75</v>
@@ -82356,9 +82370,9 @@
         <v>722</v>
       </c>
     </row>
-    <row r="281" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A281" s="18" t="s">
-        <v>166</v>
+    <row r="281" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A281" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B281" s="19">
         <v>67</v>
@@ -82652,9 +82666,9 @@
         <v>690</v>
       </c>
     </row>
-    <row r="282" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A282" s="18" t="s">
-        <v>166</v>
+    <row r="282" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A282" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B282" s="19">
         <v>67.25</v>
@@ -82948,9 +82962,9 @@
         <v>731</v>
       </c>
     </row>
-    <row r="283" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A283" s="18" t="s">
-        <v>166</v>
+    <row r="283" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A283" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B283" s="19">
         <v>67.5</v>
@@ -83244,9 +83258,9 @@
         <v>757</v>
       </c>
     </row>
-    <row r="284" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A284" s="18" t="s">
-        <v>166</v>
+    <row r="284" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A284" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B284" s="19">
         <v>67.75</v>
@@ -83540,9 +83554,9 @@
         <v>747</v>
       </c>
     </row>
-    <row r="285" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A285" s="18" t="s">
-        <v>166</v>
+    <row r="285" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A285" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B285" s="19">
         <v>68</v>
@@ -83836,9 +83850,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="286" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A286" s="18" t="s">
-        <v>166</v>
+    <row r="286" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A286" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B286" s="19">
         <v>68.25</v>
@@ -84132,9 +84146,9 @@
         <v>741</v>
       </c>
     </row>
-    <row r="287" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A287" s="18" t="s">
-        <v>166</v>
+    <row r="287" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A287" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B287" s="19">
         <v>68.5</v>
@@ -84428,9 +84442,9 @@
         <v>713</v>
       </c>
     </row>
-    <row r="288" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A288" s="18" t="s">
-        <v>166</v>
+    <row r="288" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A288" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B288" s="19">
         <v>68.75</v>
@@ -84724,9 +84738,9 @@
         <v>719</v>
       </c>
     </row>
-    <row r="289" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A289" s="18" t="s">
-        <v>166</v>
+    <row r="289" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A289" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B289" s="19">
         <v>69</v>
@@ -85020,9 +85034,9 @@
         <v>753</v>
       </c>
     </row>
-    <row r="290" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A290" s="18" t="s">
-        <v>166</v>
+    <row r="290" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A290" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B290" s="19">
         <v>69.25</v>
@@ -85316,9 +85330,9 @@
         <v>742</v>
       </c>
     </row>
-    <row r="291" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A291" s="18" t="s">
-        <v>166</v>
+    <row r="291" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A291" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B291" s="19">
         <v>69.5</v>
@@ -85612,9 +85626,9 @@
         <v>721</v>
       </c>
     </row>
-    <row r="292" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A292" s="18" t="s">
-        <v>166</v>
+    <row r="292" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A292" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B292" s="19">
         <v>69.75</v>
@@ -85908,9 +85922,9 @@
         <v>724</v>
       </c>
     </row>
-    <row r="293" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A293" s="18" t="s">
-        <v>166</v>
+    <row r="293" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A293" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B293" s="19">
         <v>70</v>
@@ -86204,9 +86218,9 @@
         <v>694</v>
       </c>
     </row>
-    <row r="294" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A294" s="18" t="s">
-        <v>166</v>
+    <row r="294" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A294" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B294" s="19">
         <v>70.25</v>
@@ -86500,9 +86514,9 @@
         <v>698</v>
       </c>
     </row>
-    <row r="295" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A295" s="18" t="s">
-        <v>166</v>
+    <row r="295" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A295" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B295" s="19">
         <v>70.5</v>
@@ -86796,9 +86810,9 @@
         <v>728</v>
       </c>
     </row>
-    <row r="296" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A296" s="18" t="s">
-        <v>166</v>
+    <row r="296" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A296" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B296" s="19">
         <v>70.75</v>
@@ -87092,9 +87106,9 @@
         <v>731</v>
       </c>
     </row>
-    <row r="297" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A297" s="18" t="s">
-        <v>166</v>
+    <row r="297" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A297" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B297" s="19">
         <v>71</v>
@@ -87388,9 +87402,9 @@
         <v>708</v>
       </c>
     </row>
-    <row r="298" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A298" s="18" t="s">
-        <v>166</v>
+    <row r="298" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A298" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B298" s="19">
         <v>71.25</v>
@@ -87684,9 +87698,9 @@
         <v>718</v>
       </c>
     </row>
-    <row r="299" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A299" s="18" t="s">
-        <v>166</v>
+    <row r="299" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A299" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B299" s="19">
         <v>71.5</v>
@@ -87980,9 +87994,9 @@
         <v>717</v>
       </c>
     </row>
-    <row r="300" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A300" s="18" t="s">
-        <v>166</v>
+    <row r="300" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A300" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B300" s="19">
         <v>71.75</v>
@@ -88276,9 +88290,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="301" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A301" s="18" t="s">
-        <v>166</v>
+    <row r="301" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A301" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="B301" s="19">
         <v>72</v>
@@ -88572,590 +88586,592 @@
         <v>721</v>
       </c>
     </row>
-    <row r="302" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A302" s="18" t="s">
+    <row r="302" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A302" s="25" t="s">
         <v>167</v>
       </c>
       <c r="B302" s="19"/>
-      <c r="C302" s="20">
-        <v>12.534000000000001</v>
-      </c>
-      <c r="D302" s="20">
-        <v>1.101</v>
-      </c>
-      <c r="E302" s="20">
-        <v>1.0780000000000001</v>
-      </c>
-      <c r="F302" s="20">
-        <v>1.663</v>
-      </c>
-      <c r="G302" s="20">
-        <v>1.157</v>
-      </c>
-      <c r="H302" s="20">
-        <v>1.2749999999999999</v>
-      </c>
-      <c r="I302" s="20">
-        <v>3.875</v>
-      </c>
-      <c r="J302" s="20">
-        <v>1.1859999999999999</v>
-      </c>
-      <c r="K302" s="20">
-        <v>1.232</v>
-      </c>
-      <c r="L302" s="20">
-        <v>1.2470000000000001</v>
-      </c>
-      <c r="M302" s="20">
-        <v>1.242</v>
-      </c>
-      <c r="N302" s="20">
-        <v>1.395</v>
-      </c>
-      <c r="O302" s="20">
-        <v>14.055999999999999</v>
-      </c>
-      <c r="P302" s="20">
-        <v>1.1439999999999999</v>
-      </c>
-      <c r="Q302" s="20">
-        <v>1.133</v>
-      </c>
-      <c r="R302" s="20">
-        <v>1.6020000000000001</v>
-      </c>
-      <c r="S302" s="20">
-        <v>1.093</v>
-      </c>
-      <c r="T302" s="20">
-        <v>1.2170000000000001</v>
-      </c>
-      <c r="U302" s="20">
-        <v>1.629</v>
-      </c>
-      <c r="V302" s="20">
-        <v>1.169</v>
-      </c>
-      <c r="W302" s="20">
-        <v>1.07</v>
-      </c>
-      <c r="X302" s="20">
-        <v>1.2929999999999999</v>
-      </c>
-      <c r="Y302" s="20">
-        <v>1.2110000000000001</v>
-      </c>
-      <c r="Z302" s="20">
-        <v>1.452</v>
-      </c>
-      <c r="AA302" s="20">
-        <v>19.718</v>
-      </c>
-      <c r="AB302" s="20">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="AC302" s="20">
-        <v>1.111</v>
-      </c>
-      <c r="AD302" s="20">
-        <v>1.6419999999999999</v>
-      </c>
-      <c r="AE302" s="20">
-        <v>1.3169999999999999</v>
-      </c>
-      <c r="AF302" s="20">
-        <v>1.234</v>
-      </c>
-      <c r="AG302" s="20">
-        <v>2.1190000000000002</v>
-      </c>
-      <c r="AH302" s="20">
-        <v>1.1539999999999999</v>
-      </c>
-      <c r="AI302" s="20">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="AJ302" s="20">
-        <v>1.266</v>
-      </c>
-      <c r="AK302" s="20">
-        <v>1.2470000000000001</v>
-      </c>
-      <c r="AL302" s="20">
-        <v>1.43</v>
-      </c>
-      <c r="AM302" s="20">
-        <v>13.858000000000001</v>
-      </c>
-      <c r="AN302" s="20">
-        <v>1.1439999999999999</v>
-      </c>
-      <c r="AO302" s="20">
-        <v>1.431</v>
-      </c>
-      <c r="AP302" s="20">
-        <v>1.8069999999999999</v>
-      </c>
-      <c r="AQ302" s="20">
-        <v>1.2929999999999999</v>
-      </c>
-      <c r="AR302" s="20">
-        <v>1.264</v>
-      </c>
-      <c r="AS302" s="20">
-        <v>3.9710000000000001</v>
-      </c>
-      <c r="AT302" s="20">
-        <v>1.2649999999999999</v>
-      </c>
-      <c r="AU302" s="20">
-        <v>1.218</v>
-      </c>
-      <c r="AV302" s="20">
-        <v>1.482</v>
-      </c>
-      <c r="AW302" s="20">
-        <v>1.232</v>
-      </c>
-      <c r="AX302" s="20">
-        <v>1.282</v>
-      </c>
-      <c r="AY302" s="20">
-        <v>2.7440000000000002</v>
-      </c>
-      <c r="AZ302" s="20">
-        <v>1.375</v>
-      </c>
-      <c r="BA302" s="20">
-        <v>1.3029999999999999</v>
-      </c>
-      <c r="BB302" s="20">
-        <v>1.2549999999999999</v>
-      </c>
-      <c r="BC302" s="20">
-        <v>1.2649999999999999</v>
-      </c>
-      <c r="BD302" s="20">
-        <v>1.323</v>
-      </c>
-      <c r="BE302" s="20">
-        <v>1.36</v>
-      </c>
-      <c r="BF302" s="20">
-        <v>1.2290000000000001</v>
-      </c>
-      <c r="BG302" s="20">
-        <v>1.222</v>
-      </c>
-      <c r="BH302" s="20">
-        <v>1.4059999999999999</v>
-      </c>
-      <c r="BI302" s="20">
-        <v>1.3120000000000001</v>
-      </c>
-      <c r="BJ302" s="20">
-        <v>1.1970000000000001</v>
-      </c>
-      <c r="BK302" s="20">
-        <v>2.286</v>
-      </c>
-      <c r="BL302" s="20">
-        <v>1.0940000000000001</v>
-      </c>
-      <c r="BM302" s="20">
-        <v>1.0549999999999999</v>
-      </c>
-      <c r="BN302" s="20">
-        <v>1.151</v>
-      </c>
-      <c r="BO302" s="20">
-        <v>1.08</v>
-      </c>
-      <c r="BP302" s="20">
-        <v>1.212</v>
-      </c>
-      <c r="BQ302" s="20">
-        <v>1.256</v>
-      </c>
-      <c r="BR302" s="20">
-        <v>1.1950000000000001</v>
-      </c>
-      <c r="BS302" s="20">
-        <v>1.117</v>
-      </c>
-      <c r="BT302" s="20">
-        <v>1.1859999999999999</v>
-      </c>
-      <c r="BU302" s="20">
-        <v>1.216</v>
-      </c>
-      <c r="BV302" s="20">
-        <v>1.153</v>
-      </c>
-      <c r="BW302" s="20">
-        <v>2.5979999999999999</v>
-      </c>
-      <c r="BX302" s="20">
-        <v>1.2190000000000001</v>
-      </c>
-      <c r="BY302" s="20">
-        <v>1.006</v>
-      </c>
-      <c r="BZ302" s="20">
-        <v>1.1779999999999999</v>
-      </c>
-      <c r="CA302" s="20">
-        <v>1.1559999999999999</v>
-      </c>
-      <c r="CB302" s="20">
-        <v>1.1910000000000001</v>
-      </c>
-      <c r="CC302" s="20">
-        <v>1.212</v>
-      </c>
-      <c r="CD302" s="20">
-        <v>1.1639999999999999</v>
-      </c>
-      <c r="CE302" s="20">
-        <v>1.121</v>
-      </c>
-      <c r="CF302" s="20">
-        <v>1.202</v>
-      </c>
-      <c r="CG302" s="20">
-        <v>1.2170000000000001</v>
-      </c>
-      <c r="CH302" s="20">
-        <v>1.3</v>
-      </c>
-      <c r="CI302" s="20">
-        <v>2.496</v>
-      </c>
-      <c r="CJ302" s="20">
-        <v>1.149</v>
-      </c>
-      <c r="CK302" s="20">
-        <v>1.036</v>
-      </c>
-      <c r="CL302" s="20">
-        <v>1.2130000000000001</v>
-      </c>
-      <c r="CM302" s="20">
-        <v>1.242</v>
-      </c>
-      <c r="CN302" s="20">
-        <v>1.121</v>
-      </c>
-      <c r="CO302" s="20">
-        <v>1.2889999999999999</v>
-      </c>
-      <c r="CP302" s="20">
-        <v>1.198</v>
-      </c>
-      <c r="CQ302" s="20">
-        <v>1.131</v>
-      </c>
-      <c r="CR302" s="20">
-        <v>1.1240000000000001</v>
-      </c>
-      <c r="CS302" s="20">
-        <v>1.3180000000000001</v>
-      </c>
-      <c r="CT302" s="6">
-        <v>1.129</v>
+      <c r="C302" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D302" s="4">
+        <v>4</v>
+      </c>
+      <c r="E302" s="4">
+        <v>4</v>
+      </c>
+      <c r="F302" s="4">
+        <v>4</v>
+      </c>
+      <c r="G302" s="4">
+        <v>4</v>
+      </c>
+      <c r="H302" s="4">
+        <v>4</v>
+      </c>
+      <c r="I302" s="4">
+        <v>4</v>
+      </c>
+      <c r="J302" s="4">
+        <v>4</v>
+      </c>
+      <c r="K302" s="4">
+        <v>4</v>
+      </c>
+      <c r="L302" s="4">
+        <v>4</v>
+      </c>
+      <c r="M302" s="4">
+        <v>4</v>
+      </c>
+      <c r="N302" s="4">
+        <v>4</v>
+      </c>
+      <c r="O302" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P302" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q302" s="4">
+        <v>4</v>
+      </c>
+      <c r="R302" s="4">
+        <v>4</v>
+      </c>
+      <c r="S302" s="4">
+        <v>4</v>
+      </c>
+      <c r="T302" s="4">
+        <v>4</v>
+      </c>
+      <c r="U302" s="4">
+        <v>4</v>
+      </c>
+      <c r="V302" s="4">
+        <v>4</v>
+      </c>
+      <c r="W302" s="4">
+        <v>4</v>
+      </c>
+      <c r="X302" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y302" s="4">
+        <v>4</v>
+      </c>
+      <c r="Z302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AA302" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AC302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AD302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AE302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AF302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AG302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AH302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AI302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AJ302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AK302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AL302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AM302" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AN302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AO302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AP302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AQ302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AR302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AS302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AT302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AU302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AV302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AW302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AX302" s="4">
+        <v>4</v>
+      </c>
+      <c r="AY302" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AZ302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BA302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BB302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BC302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BD302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BE302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BF302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BG302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BH302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BI302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BJ302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BK302" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BL302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BM302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BN302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BO302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BP302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BQ302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BR302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BS302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BT302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BU302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BV302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BW302" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BX302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BY302" s="4">
+        <v>4</v>
+      </c>
+      <c r="BZ302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CA302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CB302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CC302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CD302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CE302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CF302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CG302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CH302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CI302" s="3">
+        <v>1000</v>
+      </c>
+      <c r="CJ302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CK302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CL302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CM302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CN302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CO302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CP302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CQ302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CR302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CS302" s="4">
+        <v>4</v>
+      </c>
+      <c r="CT302" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="303" spans="1:98" x14ac:dyDescent="0.25">
-      <c r="A303" s="25"/>
+      <c r="A303" s="25" t="s">
+        <v>166</v>
+      </c>
       <c r="B303" s="19"/>
-      <c r="C303" s="20">
-        <v>11.73</v>
-      </c>
-      <c r="D303" s="20">
-        <v>72</v>
-      </c>
-      <c r="E303" s="20">
-        <v>72</v>
-      </c>
-      <c r="F303" s="20">
-        <v>72</v>
-      </c>
-      <c r="G303" s="20">
-        <v>72</v>
-      </c>
-      <c r="H303" s="20">
-        <v>72</v>
-      </c>
-      <c r="I303" s="20">
-        <v>39.92</v>
-      </c>
-      <c r="J303" s="20">
-        <v>72</v>
-      </c>
-      <c r="K303" s="20">
-        <v>72</v>
-      </c>
-      <c r="L303" s="20">
-        <v>72</v>
-      </c>
-      <c r="M303" s="20">
-        <v>72</v>
-      </c>
-      <c r="N303" s="20">
-        <v>72</v>
-      </c>
-      <c r="O303" s="20">
-        <v>9.08</v>
-      </c>
-      <c r="P303" s="20">
-        <v>72</v>
-      </c>
-      <c r="Q303" s="20">
-        <v>72</v>
-      </c>
-      <c r="R303" s="20">
-        <v>72</v>
-      </c>
-      <c r="S303" s="20">
-        <v>72</v>
-      </c>
-      <c r="T303" s="20">
-        <v>72</v>
-      </c>
-      <c r="U303" s="20">
-        <v>72</v>
-      </c>
-      <c r="V303" s="20">
-        <v>72</v>
-      </c>
-      <c r="W303" s="20">
-        <v>72</v>
-      </c>
-      <c r="X303" s="20">
-        <v>72</v>
-      </c>
-      <c r="Y303" s="20">
-        <v>72</v>
-      </c>
-      <c r="Z303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AA303" s="20">
-        <v>11.16</v>
-      </c>
-      <c r="AB303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AC303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AD303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AE303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AF303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AG303" s="20">
-        <v>69.05</v>
-      </c>
-      <c r="AH303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AI303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AJ303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AK303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AL303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AM303" s="20">
-        <v>9.66</v>
-      </c>
-      <c r="AN303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AO303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AP303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AQ303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AR303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AS303" s="20">
-        <v>38.950000000000003</v>
-      </c>
-      <c r="AT303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AU303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AV303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AW303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AX303" s="20">
-        <v>72</v>
-      </c>
-      <c r="AY303" s="20">
+      <c r="C303" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D303" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E303" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="AZ303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BA303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BB303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BC303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BD303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BE303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BF303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BG303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BH303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BI303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BJ303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BK303" s="20">
-        <v>26.67</v>
-      </c>
-      <c r="BL303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BM303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BN303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BO303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BP303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BQ303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BR303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BS303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BT303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BU303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BV303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BW303" s="20">
-        <v>20.97</v>
-      </c>
-      <c r="BX303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BY303" s="20">
-        <v>72</v>
-      </c>
-      <c r="BZ303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CA303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CB303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CC303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CD303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CE303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CF303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CG303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CH303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CI303" s="20">
-        <v>19.59</v>
-      </c>
-      <c r="CJ303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CK303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CL303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CM303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CN303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CO303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CP303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CQ303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CR303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CS303" s="20">
-        <v>72</v>
-      </c>
-      <c r="CT303" s="6">
-        <v>72</v>
+      <c r="F303" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="G303" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H303" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="I303" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J303" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="K303" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L303" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="M303" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="N303" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="O303" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="P303" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q303" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="R303" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="S303" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="T303" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="U303" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="V303" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="W303" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="X303" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y303" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z303" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA303" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB303" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC303" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD303" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE303" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF303" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG303" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH303" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI303" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ303" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK303" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="AL303" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM303" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN303" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO303" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP303" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="AQ303" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR303" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS303" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="AT303" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="AU303" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="AV303" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW303" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="AX303" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="AY303" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="AZ303" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="BA303" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB303" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="BC303" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="BD303" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="BE303" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="BF303" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="BG303" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="BH303" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="BI303" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="BJ303" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="BK303" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="BL303" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="BM303" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN303" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="BO303" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="BP303" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="BQ303" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="BR303" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS303" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="BT303" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="BU303" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="BV303" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="BW303" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="BX303" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="BY303" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="BZ303" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="CA303" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="CB303" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="CC303" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="CD303" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="CE303" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="CF303" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="CG303" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="CH303" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="CI303" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="CJ303" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="CK303" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="CL303" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="CM303" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="CN303" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="CO303" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="CP303" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="CQ303" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="CR303" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="CS303" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="CT303" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
